--- a/Pino_Market_Dashboard_Auto.xlsx
+++ b/Pino_Market_Dashboard_Auto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Watchlist" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CCE5FF"/>
         <bgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,11 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -534,6 +548,14 @@
           <t>XLK</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Microsoft</t>
@@ -547,6 +569,32 @@
       <c r="G2" t="n">
         <v>85</v>
       </c>
+      <c r="H2" t="n">
+        <v>440.84</v>
+      </c>
+      <c r="I2" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>408.31</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="M2" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>90</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>AVOID / WAIT (trend weak)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,6 +607,14 @@
           <t>XLF</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>JPMorgan</t>
@@ -572,6 +628,32 @@
       <c r="G3" t="n">
         <v>82</v>
       </c>
+      <c r="H3" t="n">
+        <v>312.48</v>
+      </c>
+      <c r="I3" t="n">
+        <v>299.88</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>298.92</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="M3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="N3" t="n">
+        <v>200</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ADD (on dip)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -584,6 +666,14 @@
           <t>XLV</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢🟢</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Eli Lilly</t>
@@ -597,6 +687,32 @@
       <c r="G4" t="n">
         <v>79</v>
       </c>
+      <c r="H4" t="n">
+        <v>1050.59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>878.6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1002</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-4.62</v>
+      </c>
+      <c r="M4" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>62</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -609,6 +725,14 @@
           <t>XLY</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>🟡🟡</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Amazon</t>
@@ -622,6 +746,29 @@
       <c r="G5" t="n">
         <v>70</v>
       </c>
+      <c r="H5" t="n">
+        <v>225.82</v>
+      </c>
+      <c r="I5" t="n">
+        <v>224.37</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K5" t="n">
+        <v>215.14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-4.73</v>
+      </c>
+      <c r="M5" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -634,6 +781,14 @@
           <t>XLC</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Alphabet</t>
@@ -647,6 +802,32 @@
       <c r="G6" t="n">
         <v>77</v>
       </c>
+      <c r="H6" t="n">
+        <v>320.15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>251.73</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="K6" t="n">
+        <v>303.94</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -659,6 +840,14 @@
           <t>XLP</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>🟡🟡</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Procter &amp; Gamble</t>
@@ -672,6 +861,32 @@
       <c r="G7" t="n">
         <v>80</v>
       </c>
+      <c r="H7" t="n">
+        <v>151.61</v>
+      </c>
+      <c r="I7" t="n">
+        <v>153.79</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="K7" t="n">
+        <v>157.86</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M7" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>265</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>AVOID / WAIT (trend weak)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -684,6 +899,14 @@
           <t>XLE</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢🟢</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Exxon Mobil</t>
@@ -697,6 +920,32 @@
       <c r="G8" t="n">
         <v>80</v>
       </c>
+      <c r="H8" t="n">
+        <v>136.71</v>
+      </c>
+      <c r="I8" t="n">
+        <v>118.14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="K8" t="n">
+        <v>149.71</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="M8" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>271</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -709,6 +958,14 @@
           <t>XLI</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢🟢</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Caterpillar</t>
@@ -722,6 +979,32 @@
       <c r="G9" t="n">
         <v>80</v>
       </c>
+      <c r="H9" t="n">
+        <v>672.14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>513</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="K9" t="n">
+        <v>740.55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="M9" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>84</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -734,6 +1017,14 @@
           <t>XLU</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>🟡🟡</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>NextEra Energy</t>
@@ -747,6 +1038,32 @@
       <c r="G10" t="n">
         <v>74</v>
       </c>
+      <c r="H10" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="K10" t="n">
+        <v>92.72</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="M10" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>269</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -759,6 +1076,14 @@
           <t>XLRE</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Prologis</t>
@@ -772,6 +1097,32 @@
       <c r="G11" t="n">
         <v>78</v>
       </c>
+      <c r="H11" t="n">
+        <v>133.31</v>
+      </c>
+      <c r="I11" t="n">
+        <v>119.36</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="K11" t="n">
+        <v>138.34</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M11" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>304</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -784,6 +1135,14 @@
           <t>XLB</t>
         </is>
       </c>
+      <c r="C12" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢🟢</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Linde</t>
@@ -796,6 +1155,32 @@
       </c>
       <c r="G12" t="n">
         <v>83</v>
+      </c>
+      <c r="H12" t="n">
+        <v>457.79</v>
+      </c>
+      <c r="I12" t="n">
+        <v>455.73</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K12" t="n">
+        <v>499.28</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="M12" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>128</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -916,17 +1301,40 @@
           <t>XLK</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>264.88</v>
+      </c>
+      <c r="F2" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J2" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>39</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -944,17 +1352,40 @@
           <t>XLK</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>186.07</v>
+      </c>
+      <c r="F3" t="n">
+        <v>175.68</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="H3" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="J3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>🟢🟢</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ADD (on dip)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -972,50 +1403,43 @@
           <t>XLP</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-    </row>
+      <c r="E4" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>260</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>🟡🟡</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>HOLD / WAIT FOR DIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
